--- a/stories/arbres/TREE-DIF-046.xlsx
+++ b/stories/arbres/TREE-DIF-046.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Adam est avec maman, au marché. Adam a envie de jouer. maman est là, tout près. On va apprendre : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam écoute maman. Adam entend les mots : laisser le temps.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Adam va vers le bac à sable. La couverture est douce. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Adam se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On montre du doigt, sans courir. maman dit : je suis là. On reste ensemble.</t>
+          <t>Adam va vers le bac à sable. La couverture est douce. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Adam se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le bac à sable. La couverture est douce. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Adam se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On montre du doigt, sans courir.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Laisser le temps à l'autre de finir sa phrase.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : attendre la fin de la phrase. Adam respire. Adam retient : laisser le temps. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le ballon. Ça sent le pain chaud. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Adam répète tout bas : laisser le temps. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2586,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2755,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Tom. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Léa. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Sami. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3757,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le seau. Le vent est doux. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Adam répète tout bas : laisser le temps. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3950,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4119,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Tom. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4286,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4453,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Léa. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4620,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4787,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Sami. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4954,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5121,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le doudou. Le sol est un peu froid. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Adam répète tout bas : laisser le temps. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5314,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5483,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Tom. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5650,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5817,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. La lumière est claire. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Léa. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5984,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6151,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Sami. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6318,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6179,7 +6347,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Adam va vers le toboggan. On entend un oiseau. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Adam se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On rit un peu. maman dit : je suis là. On reste ensemble.</t>
+          <t>Adam va vers le toboggan. On entend un oiseau. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Adam se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6317,6 +6485,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le toboggan. On entend un oiseau. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Adam se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On rit un peu.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6671,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Laisser le temps à l'autre de finir sa phrase.</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6844,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : attendre la fin de la phrase. Adam respire. Adam retient : laisser le temps. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6851,6 +7035,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7013,6 +7202,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le ballon. Une feuille tombe. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Adam répète tout bas : laisser le temps. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7201,6 +7395,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7365,6 +7564,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Tom. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7527,6 +7731,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7689,6 +7898,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Léa. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7851,6 +8065,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8013,6 +8232,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. La lumière est claire. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Sami. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8175,6 +8399,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8337,6 +8566,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le seau. L'eau coule, tout petit bruit. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Adam répète tout bas : laisser le temps. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8525,6 +8759,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8689,6 +8928,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Tom. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8851,6 +9095,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9013,6 +9262,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Léa. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9175,6 +9429,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9337,6 +9596,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Sami. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9499,6 +9763,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9661,6 +9930,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le doudou. Un vélo passe au loin. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Adam répète tout bas : laisser le temps. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9849,6 +10123,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10013,6 +10292,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. La lumière est claire. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Tom. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10175,6 +10459,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10337,6 +10626,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Léa. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10499,6 +10793,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10661,6 +10960,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Sami. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10823,6 +11127,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10847,7 +11156,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Adam va vers les balançoires. Ça sent le pain chaud. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Adam se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On se tait une seconde. maman dit : je suis là. On reste ensemble.</t>
+          <t>Adam va vers les balançoires. Ça sent le pain chaud. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Adam se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On se tait une seconde. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10985,6 +11294,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers les balançoires. Ça sent le pain chaud. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Adam se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On se tait une seconde.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11165,6 +11480,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Laisser le temps à l'autre de finir sa phrase.</t>
         </is>
       </c>
     </row>
@@ -11333,6 +11653,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : attendre la fin de la phrase. Adam respire. Adam retient : laisser le temps. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11519,6 +11844,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11681,6 +12011,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le ballon. La lumière est claire. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Adam répète tout bas : laisser le temps. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11869,6 +12204,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12033,6 +12373,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Tom. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12195,6 +12540,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12357,6 +12707,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. La lumière est claire. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Léa. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12519,6 +12874,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12681,6 +13041,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Sami. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12843,6 +13208,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13005,6 +13375,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le seau. Il y a des miettes sur la table. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Adam répète tout bas : laisser le temps. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13193,6 +13568,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13357,6 +13737,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. La lumière est claire. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Tom. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13519,6 +13904,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13681,6 +14071,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Léa. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13843,6 +14238,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14005,6 +14405,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. Un chat miaule une fois. On range un objet. Cette fin-là est celle de les balançoires, le seau et Sami. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14167,6 +14572,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14329,6 +14739,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le doudou. Un chat miaule une fois. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Adam répète tout bas : laisser le temps. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14517,6 +14932,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14681,6 +15101,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Tom. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Tom. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14843,6 +15268,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15005,6 +15435,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Léa. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Léa. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15167,6 +15602,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15329,6 +15769,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint Sami. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Sami. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15491,6 +15936,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15509,7 +15959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15582,6 +16032,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-046.xlsx
+++ b/stories/arbres/TREE-DIF-046.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Adam est avec maman, au marché. Adam a envie de jouer. maman est là, tout près. On va apprendre : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam écoute maman. Adam entend les mots : laisser le temps.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Laisser le temps à l'autre de finir sa phrase.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : attendre la fin de la phrase. Adam respire. Adam retient : laisser le temps. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Adam a choisi le ballon. Ça sent le pain chaud. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Adam répète tout bas : laisser le temps. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2605,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2773,7 @@
           <t>narrateur|Adam rejoint Tom. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Tom. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3109,7 @@
           <t>narrateur|Adam rejoint Léa. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Léa. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3445,7 @@
           <t>narrateur|Adam rejoint Sami. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Sami. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3781,7 @@
           <t>narrateur|Adam a choisi le seau. Le vent est doux. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Adam répète tout bas : laisser le temps. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3957,6 +3977,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4145,7 @@
           <t>narrateur|Adam rejoint Tom. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Tom. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4458,6 +4481,7 @@
           <t>narrateur|Adam rejoint Léa. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Léa. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4625,6 +4649,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4792,6 +4817,7 @@
           <t>narrateur|Adam rejoint Sami. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Sami. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4959,6 +4985,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5126,6 +5153,7 @@
           <t>narrateur|Adam a choisi le doudou. Le sol est un peu froid. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Adam répète tout bas : laisser le temps. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5321,6 +5349,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5488,6 +5517,7 @@
           <t>narrateur|Adam rejoint Tom. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Tom. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5655,6 +5685,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5822,6 +5853,7 @@
           <t>narrateur|Adam rejoint Léa. La lumière est claire. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Léa. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5989,6 +6021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6156,6 +6189,7 @@
           <t>narrateur|Adam rejoint Sami. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Sami. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6323,6 +6357,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6491,6 +6526,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6678,6 +6714,7 @@
           <t>narrateur|Que fait-on ? Laisser le temps à l'autre de finir sa phrase.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6849,6 +6886,7 @@
           <t>narrateur|Oui. Voici le geste : attendre la fin de la phrase. Adam respire. Adam retient : laisser le temps. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7040,6 +7078,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7207,6 +7246,7 @@
           <t>narrateur|Adam a choisi le ballon. Une feuille tombe. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Adam répète tout bas : laisser le temps. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7402,6 +7442,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7569,6 +7610,7 @@
           <t>narrateur|Adam rejoint Tom. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Tom. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7736,6 +7778,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7903,6 +7946,7 @@
           <t>narrateur|Adam rejoint Léa. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Léa. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8070,6 +8114,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8237,6 +8282,7 @@
           <t>narrateur|Adam rejoint Sami. La lumière est claire. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Sami. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8404,6 +8450,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8571,6 +8618,7 @@
           <t>narrateur|Adam a choisi le seau. L'eau coule, tout petit bruit. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Adam répète tout bas : laisser le temps. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8766,6 +8814,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8933,6 +8982,7 @@
           <t>narrateur|Adam rejoint Tom. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Tom. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9100,6 +9150,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9267,6 +9318,7 @@
           <t>narrateur|Adam rejoint Léa. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Léa. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9434,6 +9486,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9601,6 +9654,7 @@
           <t>narrateur|Adam rejoint Sami. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Sami. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9768,6 +9822,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9935,6 +9990,7 @@
           <t>narrateur|Adam a choisi le doudou. Un vélo passe au loin. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Adam répète tout bas : laisser le temps. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10130,6 +10186,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10297,6 +10354,7 @@
           <t>narrateur|Adam rejoint Tom. La lumière est claire. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Tom. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10464,6 +10522,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10631,6 +10690,7 @@
           <t>narrateur|Adam rejoint Léa. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Léa. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10798,6 +10858,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10965,6 +11026,7 @@
           <t>narrateur|Adam rejoint Sami. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Sami. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11132,6 +11194,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11300,6 +11363,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11487,6 +11551,7 @@
           <t>narrateur|Que fait-on ? Laisser le temps à l'autre de finir sa phrase.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11658,6 +11723,7 @@
           <t>narrateur|Oui. Voici le geste : attendre la fin de la phrase. Adam respire. Adam retient : laisser le temps. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11849,6 +11915,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12016,6 +12083,7 @@
           <t>narrateur|Adam a choisi le ballon. La lumière est claire. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Adam répète tout bas : laisser le temps. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12211,6 +12279,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12378,6 +12447,7 @@
           <t>narrateur|Adam rejoint Tom. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Tom. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12545,6 +12615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12712,6 +12783,7 @@
           <t>narrateur|Adam rejoint Léa. La lumière est claire. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Léa. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12879,6 +12951,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13046,6 +13119,7 @@
           <t>narrateur|Adam rejoint Sami. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Sami. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13213,6 +13287,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13380,6 +13455,7 @@
           <t>narrateur|Adam a choisi le seau. Il y a des miettes sur la table. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Adam répète tout bas : laisser le temps. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13575,6 +13651,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13742,6 +13819,7 @@
           <t>narrateur|Adam rejoint Tom. La lumière est claire. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Tom. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13909,6 +13987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14076,6 +14155,7 @@
           <t>narrateur|Adam rejoint Léa. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Léa. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14243,6 +14323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14410,6 +14491,7 @@
           <t>narrateur|Adam rejoint Sami. Un chat miaule une fois. On range un objet. Cette fin-là est celle de les balançoires, le seau et Sami. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14577,6 +14659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14744,6 +14827,7 @@
           <t>narrateur|Adam a choisi le doudou. Un chat miaule une fois. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Adam répète tout bas : laisser le temps. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14939,6 +15023,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15106,6 +15191,7 @@
           <t>narrateur|Adam rejoint Tom. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Tom. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15273,6 +15359,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15440,6 +15527,7 @@
           <t>narrateur|Adam rejoint Léa. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Léa. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15607,6 +15695,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15774,6 +15863,7 @@
           <t>narrateur|Adam rejoint Sami. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Sami. Adam a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Adam a entendu : laisser le temps. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15941,6 +16031,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15959,7 +16050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16039,6 +16130,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16053,7 +16158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16240,6 +16345,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-046.xlsx
+++ b/stories/arbres/TREE-DIF-046.xlsx
@@ -2307,12 +2307,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Le panier arrive près de l'étal de papier. Le panier bute contre une caisse de papier. Des moulinets pendent, tous mêlés. C'est ici ? C'est le rouge, près du. Le mot s'arrête au milieu. Près du quoi ? Victorino referme sa bouche, tout net. Ils se ressemblent tous, là-haut. On fait comment, Victorino ?</t>
+          <t>Le panier arrive près de l'étal de papier. Il bute contre une caisse de papier. Des moulinets pendent, tous mêlés. C'est ici ? C'est le rouge, près du. Le mot s'arrête au milieu. Près du quoi ? Victorino referme sa bouche, tout net. Ils se ressemblent tous, là-haut. On fait comment, Victorino ?</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Le panier arrive près de l'étal de papier. Le panier bute contre une caisse de papier. Des moulinets pendent, tous mêlés. C'est ici ? C'est le rouge, près du. Le mot s'arrête au milieu. Près du quoi ? Victorino referme sa bouche, tout net. Ils se ressemblent tous, là-haut. On fait comment, Victorino ?</t>
+          <t>Le panier arrive près de l'étal de papier. Il bute contre une caisse de papier. Des moulinets pendent, tous mêlés. C'est ici ? C'est le rouge, près du. Le mot s'arrête au milieu. Près du quoi ? Victorino referme sa bouche, tout net. Ils se ressemblent tous, là-haut. On fait comment, Victorino ?</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2448,7 +2448,7 @@
       <c r="AW8" t="inlineStr">
         <is>
           <t>narrateur|Le panier arrive près de l'étal de papier.
-narrateur|Le panier bute contre une caisse de papier.
+narrateur|Il bute contre une caisse de papier.
 narrateur|Des moulinets pendent, tous mêlés.
 enfant-m|C'est ici ?
 papa|C'est le rouge, près du.
@@ -3726,12 +3726,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Le panier arrive près de la fontaine. Le panier se mouille un peu, au bord. Il est là-dedans, le rouge ? Il est près de l'. L'eau couvre le mot, tout fort. Des gouttes tapent le bord, déjà. Près de l'eau ? Victorino recule d'un pas, puis attend. On n'entend plus la fin. Tu trouves comment ?</t>
+          <t>Le panier arrive près de la fontaine. Il se mouille un peu, au bord. Il est là, le rouge ? Il est près de l'. L'eau couvre le mot, tout fort. Des gouttes tapent le bord, déjà. Près de l'eau ? Victorino recule d'un pas, puis attend. On n'entend plus la fin. Tu trouves comment ?</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Le panier arrive près de la fontaine. Le panier se mouille un peu, au bord. Il est là-dedans, le rouge ? Il est près de l'. L'eau couvre le mot, tout fort. Des gouttes tapent le bord, déjà. Près de l'eau ? Victorino recule d'un pas, puis attend. On n'entend plus la fin. Tu trouves comment ?</t>
+          <t>Le panier arrive près de la fontaine. Il se mouille un peu, au bord. Il est là, le rouge ? Il est près de l'. L'eau couvre le mot, tout fort. Des gouttes tapent le bord, déjà. Près de l'eau ? Victorino recule d'un pas, puis attend. On n'entend plus la fin. Tu trouves comment ?</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3867,8 +3867,8 @@
       <c r="AW16" t="inlineStr">
         <is>
           <t>narrateur|Le panier arrive près de la fontaine.
-narrateur|Le panier se mouille un peu, au bord.
-enfant-m|Il est là-dedans, le rouge ?
+narrateur|Il se mouille un peu, au bord.
+enfant-m|Il est là, le rouge ?
 maman|Il est près de l'.
 narrateur|L'eau couvre le mot, tout fort.
 narrateur|Des gouttes tapent le bord, déjà.
@@ -4273,12 +4273,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Loin de l'eau, le rouge était là. Tu as fini, papa. Oui, le mot était long. Merci d'avoir reculé sans crier. Le panier tient le bâton, tout droit. Une goutte sèche déjà sur le bâton. Victorino fait tourner le rouge, tout près. La fontaine redevient une fontaine, tout simple.</t>
+          <t>Loin de l'eau, le rouge était là. Tu as fini, papa. Oui, le mot était long. Tu as reculé, tout doux. Le panier tient le bâton, tout droit. Une goutte sèche déjà sur le bâton. Victorino fait tourner le rouge, tout près. La fontaine redevient une fontaine, tout simple.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Loin de l'eau, le rouge était là. Tu as fini, papa. Oui, le mot était long. Merci d'avoir reculé sans crier. Le panier tient le bâton, tout droit. Une goutte sèche déjà sur le bâton. Victorino fait tourner le rouge, tout près. La fontaine redevient une fontaine, tout simple.</t>
+          <t>Loin de l'eau, le rouge était là. Tu as fini, papa. Oui, le mot était long. Tu as reculé, tout doux. Le panier tient le bâton, tout droit. Une goutte sèche déjà sur le bâton. Victorino fait tourner le rouge, tout près. La fontaine redevient une fontaine, tout simple.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
           <t>narrateur|Loin de l'eau, le rouge était là.
 enfant-m|Tu as fini, papa.
 papa|Oui, le mot était long.
-maman|Merci d'avoir reculé sans crier.
+maman|Tu as reculé, tout doux.
 narrateur|Le panier tient le bâton, tout droit.
 narrateur|Une goutte sèche déjà sur le bâton.
 narrateur|Victorino fait tourner le rouge, tout près.
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Le panier arrive sous l'auvent bleu. Le panier lève le nez, trop bas encore. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du bord ? Victorino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Tu fais quoi, alors ?</t>
+          <t>Le panier arrive sous l'auvent bleu. Il reste trop bas, encore. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du bord ? Victorino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Tu fais quoi, alors ?</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Le panier arrive sous l'auvent bleu. Le panier lève le nez, trop bas encore. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du bord ? Victorino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Tu fais quoi, alors ?</t>
+          <t>Le panier arrive sous l'auvent bleu. Il reste trop bas, encore. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du bord ? Victorino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Tu fais quoi, alors ?</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       <c r="AW24" t="inlineStr">
         <is>
           <t>narrateur|Le panier arrive sous l'auvent bleu.
-narrateur|Le panier lève le nez, trop bas encore.
+narrateur|Il reste trop bas, encore.
 enfant-m|Tout en haut ?
 papa|Tout en haut, près du.
 narrateur|Papa s'arrête, les lèvres encore rondes.
@@ -7300,12 +7300,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>La ficelle arrive près de l'étal de papier. La ficelle s'accroche à un clou, déjà. Des moulinets pendent, tous mêlés. C'est ici ? C'est le rouge, près du. Le mot s'arrête au milieu. Près du quoi ? Victorino referme sa bouche, tout net. Ils se ressemblent tous, là-haut. On fait comment, Victorino ?</t>
+          <t>La ficelle arrive près de l'étal de papier. Elle s'accroche à un clou, déjà. Des moulinets pendent, tous mêlés. C'est ici ? C'est le rouge, près du. Le mot s'arrête au milieu. Près du quoi ? Victorino referme sa bouche, tout net. Ils se ressemblent tous, là-haut. On fait comment, Victorino ?</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>La ficelle arrive près de l'étal de papier. La ficelle s'accroche à un clou, déjà. Des moulinets pendent, tous mêlés. C'est ici ? C'est le rouge, près du. Le mot s'arrête au milieu. Près du quoi ? Victorino referme sa bouche, tout net. Ils se ressemblent tous, là-haut. On fait comment, Victorino ?</t>
+          <t>La ficelle arrive près de l'étal de papier. Elle s'accroche à un clou, déjà. Des moulinets pendent, tous mêlés. C'est ici ? C'est le rouge, près du. Le mot s'arrête au milieu. Près du quoi ? Victorino referme sa bouche, tout net. Ils se ressemblent tous, là-haut. On fait comment, Victorino ?</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       <c r="AW36" t="inlineStr">
         <is>
           <t>narrateur|La ficelle arrive près de l'étal de papier.
-narrateur|La ficelle s'accroche à un clou, déjà.
+narrateur|Elle s'accroche à un clou, déjà.
 narrateur|Des moulinets pendent, tous mêlés.
 enfant-m|C'est ici ?
 papa|C'est le rouge, près du.
@@ -8719,12 +8719,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>La ficelle arrive près de la fontaine. La ficelle boit une goutte, tout net. Il est là-dedans, le rouge ? Il est près de l'. L'eau couvre le mot, tout fort. Des gouttes tapent le bord, déjà. Près de l'eau ? Victorino recule d'un pas, puis attend. On n'entend plus la fin. Tu trouves comment ?</t>
+          <t>La ficelle arrive près de la fontaine. Elle boit une goutte, tout net. Il est là, le rouge ? Il est près de l'. L'eau couvre le mot, tout fort. Des gouttes tapent le bord, déjà. Près de l'eau ? Victorino recule d'un pas, puis attend. On n'entend plus la fin. Tu trouves comment ?</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>La ficelle arrive près de la fontaine. La ficelle boit une goutte, tout net. Il est là-dedans, le rouge ? Il est près de l'. L'eau couvre le mot, tout fort. Des gouttes tapent le bord, déjà. Près de l'eau ? Victorino recule d'un pas, puis attend. On n'entend plus la fin. Tu trouves comment ?</t>
+          <t>La ficelle arrive près de la fontaine. Elle boit une goutte, tout net. Il est là, le rouge ? Il est près de l'. L'eau couvre le mot, tout fort. Des gouttes tapent le bord, déjà. Près de l'eau ? Victorino recule d'un pas, puis attend. On n'entend plus la fin. Tu trouves comment ?</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -8860,8 +8860,8 @@
       <c r="AW44" t="inlineStr">
         <is>
           <t>narrateur|La ficelle arrive près de la fontaine.
-narrateur|La ficelle boit une goutte, tout net.
-enfant-m|Il est là-dedans, le rouge ?
+narrateur|Elle boit une goutte, tout net.
+enfant-m|Il est là, le rouge ?
 maman|Il est près de l'.
 narrateur|L'eau couvre le mot, tout fort.
 narrateur|Des gouttes tapent le bord, déjà.
@@ -9266,12 +9266,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Loin de l'eau, le rouge était là. Tu as fini, papa. Oui, le mot était long. Merci d'avoir reculé sans crier. La ficelle serre le bois, tout net. Une goutte sèche déjà sur le bâton. Victorino fait tourner le rouge, tout près. La fontaine redevient une fontaine, tout simple.</t>
+          <t>Loin de l'eau, le rouge était là. Tu as fini, papa. Oui, le mot était long. Tu as reculé, tout doux. La ficelle serre le bois, tout net. Une goutte sèche déjà sur le bâton. Victorino fait tourner le rouge, tout près. La fontaine redevient une fontaine, tout simple.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Loin de l'eau, le rouge était là. Tu as fini, papa. Oui, le mot était long. Merci d'avoir reculé sans crier. La ficelle serre le bois, tout net. Une goutte sèche déjà sur le bâton. Victorino fait tourner le rouge, tout près. La fontaine redevient une fontaine, tout simple.</t>
+          <t>Loin de l'eau, le rouge était là. Tu as fini, papa. Oui, le mot était long. Tu as reculé, tout doux. La ficelle serre le bois, tout net. Une goutte sèche déjà sur le bâton. Victorino fait tourner le rouge, tout près. La fontaine redevient une fontaine, tout simple.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -9409,7 +9409,7 @@
           <t>narrateur|Loin de l'eau, le rouge était là.
 enfant-m|Tu as fini, papa.
 papa|Oui, le mot était long.
-maman|Merci d'avoir reculé sans crier.
+maman|Tu as reculé, tout doux.
 narrateur|La ficelle serre le bois, tout net.
 narrateur|Une goutte sèche déjà sur le bâton.
 narrateur|Victorino fait tourner le rouge, tout près.
@@ -10138,12 +10138,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>La ficelle arrive sous l'auvent bleu. La ficelle pend, trop courte, sous le bleu. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du bord ? Victorino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Tu fais quoi, alors ?</t>
+          <t>La ficelle arrive sous l'auvent bleu. Elle pend, trop courte, sous le bleu. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du bord ? Victorino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Tu fais quoi, alors ?</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>La ficelle arrive sous l'auvent bleu. La ficelle pend, trop courte, sous le bleu. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du bord ? Victorino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Tu fais quoi, alors ?</t>
+          <t>La ficelle arrive sous l'auvent bleu. Elle pend, trop courte, sous le bleu. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du bord ? Victorino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Tu fais quoi, alors ?</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -10279,7 +10279,7 @@
       <c r="AW52" t="inlineStr">
         <is>
           <t>narrateur|La ficelle arrive sous l'auvent bleu.
-narrateur|La ficelle pend, trop courte, sous le bleu.
+narrateur|Elle pend, trop courte, sous le bleu.
 enfant-m|Tout en haut ?
 papa|Tout en haut, près du.
 narrateur|Papa s'arrête, les lèvres encore rondes.
@@ -12293,12 +12293,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>La bourse arrive près de l'étal de papier. La bourse tape le bois, un petit toc. Des moulinets pendent, tous mêlés. C'est ici ? C'est le rouge, près du. Le mot s'arrête au milieu. Près du quoi ? Victorino referme sa bouche, tout net. Ils se ressemblent tous, là-haut. On fait comment, Victorino ?</t>
+          <t>La bourse arrive près de l'étal de papier. Elle tape le bois, un petit toc. Des moulinets pendent, tous mêlés. C'est ici ? C'est le rouge, près du. Le mot s'arrête au milieu. Près du quoi ? Victorino referme sa bouche, tout net. Ils se ressemblent tous, là-haut. On fait comment, Victorino ?</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>La bourse arrive près de l'étal de papier. La bourse tape le bois, un petit toc. Des moulinets pendent, tous mêlés. C'est ici ? C'est le rouge, près du. Le mot s'arrête au milieu. Près du quoi ? Victorino referme sa bouche, tout net. Ils se ressemblent tous, là-haut. On fait comment, Victorino ?</t>
+          <t>La bourse arrive près de l'étal de papier. Elle tape le bois, un petit toc. Des moulinets pendent, tous mêlés. C'est ici ? C'est le rouge, près du. Le mot s'arrête au milieu. Près du quoi ? Victorino referme sa bouche, tout net. Ils se ressemblent tous, là-haut. On fait comment, Victorino ?</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -12434,7 +12434,7 @@
       <c r="AW64" t="inlineStr">
         <is>
           <t>narrateur|La bourse arrive près de l'étal de papier.
-narrateur|La bourse tape le bois, un petit toc.
+narrateur|Elle tape le bois, un petit toc.
 narrateur|Des moulinets pendent, tous mêlés.
 enfant-m|C'est ici ?
 papa|C'est le rouge, près du.
@@ -13712,12 +13712,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>La bourse arrive près de la fontaine. La bourse cliquette sous l'eau qui vole. Il est là-dedans, le rouge ? Il est près de l'. L'eau couvre le mot, tout fort. Des gouttes tapent le bord, déjà. Près de l'eau ? Victorino recule d'un pas, puis attend. On n'entend plus la fin. Tu trouves comment ?</t>
+          <t>La bourse arrive près de la fontaine. Elle cliquette sous l'eau qui vole. Il est là, le rouge ? Il est près de l'. L'eau couvre le mot, tout fort. Des gouttes tapent le bord, déjà. Près de l'eau ? Victorino recule d'un pas, puis attend. On n'entend plus la fin. Tu trouves comment ?</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>La bourse arrive près de la fontaine. La bourse cliquette sous l'eau qui vole. Il est là-dedans, le rouge ? Il est près de l'. L'eau couvre le mot, tout fort. Des gouttes tapent le bord, déjà. Près de l'eau ? Victorino recule d'un pas, puis attend. On n'entend plus la fin. Tu trouves comment ?</t>
+          <t>La bourse arrive près de la fontaine. Elle cliquette sous l'eau qui vole. Il est là, le rouge ? Il est près de l'. L'eau couvre le mot, tout fort. Des gouttes tapent le bord, déjà. Près de l'eau ? Victorino recule d'un pas, puis attend. On n'entend plus la fin. Tu trouves comment ?</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -13853,8 +13853,8 @@
       <c r="AW72" t="inlineStr">
         <is>
           <t>narrateur|La bourse arrive près de la fontaine.
-narrateur|La bourse cliquette sous l'eau qui vole.
-enfant-m|Il est là-dedans, le rouge ?
+narrateur|Elle cliquette sous l'eau qui vole.
+enfant-m|Il est là, le rouge ?
 maman|Il est près de l'.
 narrateur|L'eau couvre le mot, tout fort.
 narrateur|Des gouttes tapent le bord, déjà.
@@ -14259,12 +14259,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Loin de l'eau, le rouge était là. Tu as fini, papa. Oui, le mot était long. Merci d'avoir reculé sans crier. La bourse cliquette une fois, puis se tait. Une goutte sèche déjà sur le bâton. Victorino fait tourner le rouge, tout près. La fontaine redevient une fontaine, tout simple.</t>
+          <t>Loin de l'eau, le rouge était là. Tu as fini, papa. Oui, le mot était long. Tu as reculé, tout doux. La bourse cliquette une fois, puis se tait. Une goutte sèche déjà sur le bâton. Victorino fait tourner le rouge, tout près. La fontaine redevient une fontaine, tout simple.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Loin de l'eau, le rouge était là. Tu as fini, papa. Oui, le mot était long. Merci d'avoir reculé sans crier. La bourse cliquette une fois, puis se tait. Une goutte sèche déjà sur le bâton. Victorino fait tourner le rouge, tout près. La fontaine redevient une fontaine, tout simple.</t>
+          <t>Loin de l'eau, le rouge était là. Tu as fini, papa. Oui, le mot était long. Tu as reculé, tout doux. La bourse cliquette une fois, puis se tait. Une goutte sèche déjà sur le bâton. Victorino fait tourner le rouge, tout près. La fontaine redevient une fontaine, tout simple.</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -14402,7 +14402,7 @@
           <t>narrateur|Loin de l'eau, le rouge était là.
 enfant-m|Tu as fini, papa.
 papa|Oui, le mot était long.
-maman|Merci d'avoir reculé sans crier.
+maman|Tu as reculé, tout doux.
 narrateur|La bourse cliquette une fois, puis se tait.
 narrateur|Une goutte sèche déjà sur le bâton.
 narrateur|Victorino fait tourner le rouge, tout près.
@@ -15131,12 +15131,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>La bourse arrive sous l'auvent bleu. La bourse n'atteint pas le bord, trop haute. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du bord ? Victorino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Tu fais quoi, alors ?</t>
+          <t>La bourse arrive sous l'auvent bleu. Elle n'atteint pas le bord, trop haute. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du bord ? Victorino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Tu fais quoi, alors ?</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>La bourse arrive sous l'auvent bleu. La bourse n'atteint pas le bord, trop haute. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du bord ? Victorino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Tu fais quoi, alors ?</t>
+          <t>La bourse arrive sous l'auvent bleu. Elle n'atteint pas le bord, trop haute. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du bord ? Victorino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Tu fais quoi, alors ?</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -15272,7 +15272,7 @@
       <c r="AW80" t="inlineStr">
         <is>
           <t>narrateur|La bourse arrive sous l'auvent bleu.
-narrateur|La bourse n'atteint pas le bord, trop haute.
+narrateur|Elle n'atteint pas le bord, trop haute.
 enfant-m|Tout en haut ?
 papa|Tout en haut, près du.
 narrateur|Papa s'arrête, les lèvres encore rondes.
@@ -16544,7 +16544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16643,6 +16643,13 @@
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
